--- a/test/configs/data/develop/pypsaeur_backup_sector_coupled_simp.xlsx
+++ b/test/configs/data/develop/pypsaeur_backup_sector_coupled_simp.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7824" firstSheet="1" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="7824" firstSheet="1" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Carrier" sheetId="1" r:id="rId1"/>
@@ -23,6 +23,10 @@
     <sheet name="loads_t_p_set" sheetId="9" r:id="rId9"/>
     <sheet name="snapshots" sheetId="11" r:id="rId10"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Link!$A$1:$BB$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Store!$A$1:$AD$1</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -33,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="187">
   <si>
     <t>co2_emissions</t>
   </si>
@@ -212,13 +216,7 @@
     <t>IT0 0</t>
   </si>
   <si>
-    <t>Slack</t>
-  </si>
-  <si>
     <t>IT</t>
-  </si>
-  <si>
-    <t>IT1 0</t>
   </si>
   <si>
     <t>PQ</t>
@@ -329,9 +327,6 @@
     <t>p_nom_opt</t>
   </si>
   <si>
-    <t>IT0 0 CCGT</t>
-  </si>
-  <si>
     <t>False</t>
   </si>
   <si>
@@ -372,15 +367,6 @@
   </si>
   <si>
     <t>underwater_fraction</t>
-  </si>
-  <si>
-    <t>relation/8185711-500-DC</t>
-  </si>
-  <si>
-    <t>relation/8185711</t>
-  </si>
-  <si>
-    <t>LINESTRING (8.306507186431089 40.84110865715793, 8.3065975 40.8410218, 8.3076221 40.8404009, 8.3106852 40.8424889, 8.3135283 40.8447798, 8.3138102 40.8452217, 8.3336448 40.8763037, 8.3547585 40.919545, 8.3629986 40.9246682, 8.438959 40.9365347, 8.4637641 40.9377018, 8.4968945 40.9423702, 8.578777 40.9519001, 8.6672684 40.9695948, 8.7741276 41.0055206, 8.7916373 41.0131954, 8.8120433 41.0387725, 8.8171498 41.1805441, 8.9698212 41.2809838, 10.4425021 41.516806, 12.771601 41.3438287, 12.8105575 41.4138493, 12.8113675 41.429471, 12.8075105 41.4306293, 12.806985991114674 41.42980383291617)</t>
   </si>
   <si>
     <t>name</t>
@@ -446,16 +432,7 @@
     <t>Slack Unit</t>
   </si>
   <si>
-    <t>MWh_el</t>
-  </si>
-  <si>
     <t>EU</t>
-  </si>
-  <si>
-    <t>co2 atmosphere</t>
-  </si>
-  <si>
-    <t>t_co2</t>
   </si>
   <si>
     <t>electricity</t>
@@ -480,9 +457,6 @@
   </si>
   <si>
     <t>EU gas</t>
-  </si>
-  <si>
-    <t>IT1 0 OCGT</t>
   </si>
   <si>
     <t>H2 Store</t>
@@ -558,6 +532,72 @@
   </si>
   <si>
     <t>e_nom_opt</t>
+  </si>
+  <si>
+    <t>IT0 0 H2</t>
+  </si>
+  <si>
+    <t>IT0 0 urban central heat</t>
+  </si>
+  <si>
+    <t>urban central heat</t>
+  </si>
+  <si>
+    <t>MWh_th</t>
+  </si>
+  <si>
+    <t>EU oil</t>
+  </si>
+  <si>
+    <t>oil</t>
+  </si>
+  <si>
+    <t>EU oil primary</t>
+  </si>
+  <si>
+    <t>oil primary</t>
+  </si>
+  <si>
+    <t>EU methanol</t>
+  </si>
+  <si>
+    <t>EU shipping methanol</t>
+  </si>
+  <si>
+    <t>shipping methanol</t>
+  </si>
+  <si>
+    <t>bus4</t>
+  </si>
+  <si>
+    <t>efficiency4</t>
+  </si>
+  <si>
+    <t>energy to power ratio</t>
+  </si>
+  <si>
+    <t>IT0 0 SMR CC</t>
+  </si>
+  <si>
+    <t>SMR CC</t>
+  </si>
+  <si>
+    <t>IT0 0 urban central gas boiler</t>
+  </si>
+  <si>
+    <t>urban central gas boiler</t>
+  </si>
+  <si>
+    <t>EU oil refining</t>
+  </si>
+  <si>
+    <t>oil refining</t>
+  </si>
+  <si>
+    <t>IT0 0 methanolisation</t>
+  </si>
+  <si>
+    <t>methanolisation</t>
   </si>
 </sst>
 </file>
@@ -881,7 +921,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1072,13 +1112,13 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="B11">
         <v>0</v>
       </c>
       <c r="D11" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -1089,16 +1129,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B12">
         <v>-1</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D12" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="E12" t="s">
         <v>7</v>
@@ -1109,16 +1149,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -1129,16 +1169,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B14">
         <v>0</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="D14" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -1149,16 +1189,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="B15">
         <v>0</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="D15" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>7</v>
@@ -1209,16 +1249,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="B18">
         <v>0</v>
       </c>
       <c r="C18" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="E18" t="s">
         <v>7</v>
@@ -1249,16 +1289,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="B20">
         <v>0</v>
       </c>
       <c r="C20" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>128</v>
+        <v>122</v>
       </c>
       <c r="E20" t="s">
         <v>7</v>
@@ -1269,16 +1309,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="B21">
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D21" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
         <v>7</v>
@@ -1289,7 +1329,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -1298,7 +1338,7 @@
         <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
         <v>7</v>
@@ -1329,16 +1369,16 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="B24">
         <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>134</v>
+        <v>128</v>
       </c>
       <c r="D24" t="s">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="E24" t="s">
         <v>7</v>
@@ -1369,7 +1409,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1378,7 +1418,7 @@
         <v>35</v>
       </c>
       <c r="D26" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
         <v>7</v>
@@ -1389,16 +1429,16 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="B27">
         <v>0</v>
       </c>
       <c r="C27" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="E27" t="s">
         <v>7</v>
@@ -1409,16 +1449,16 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B28">
         <v>0</v>
       </c>
       <c r="C28" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E28" t="s">
         <v>7</v>
@@ -1439,16 +1479,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="B1" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C1" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -28002,15 +28042,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Q5"/>
+  <dimension ref="A1:Q8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
         <v>42</v>
@@ -28063,25 +28103,25 @@
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="B2">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>11.861807419676801</v>
+        <v>-5.5</v>
       </c>
       <c r="E2">
-        <v>43.502700216278299</v>
+        <v>46</v>
       </c>
       <c r="F2" t="s">
-        <v>5</v>
+        <v>118</v>
       </c>
       <c r="G2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H2" t="s">
-        <v>58</v>
+        <v>131</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -28093,42 +28133,30 @@
         <v>7</v>
       </c>
       <c r="L2" t="s">
-        <v>59</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
         <v>60</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>165</v>
       </c>
       <c r="B3">
-        <v>380</v>
+        <v>1</v>
       </c>
       <c r="D3">
-        <v>8.7398246778425897</v>
+        <v>11.861807419676801</v>
       </c>
       <c r="E3">
-        <v>40.032889929774797</v>
+        <v>43.502700216278299</v>
       </c>
       <c r="F3" t="s">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="H3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -28140,42 +28168,33 @@
         <v>7</v>
       </c>
       <c r="L3" t="s">
+        <v>60</v>
+      </c>
+      <c r="O3" t="s">
         <v>59</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3" t="s">
-        <v>60</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>139</v>
+        <v>166</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="D4">
-        <v>-5.5</v>
+        <v>11.861807419676801</v>
       </c>
       <c r="E4">
-        <v>46</v>
+        <v>43.502700216278299</v>
       </c>
       <c r="F4" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G4" t="s">
-        <v>140</v>
+        <v>168</v>
       </c>
       <c r="H4" t="s">
-        <v>138</v>
+        <v>58</v>
       </c>
       <c r="I4">
         <v>1</v>
@@ -28187,12 +28206,15 @@
         <v>7</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+      <c r="O4" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>148</v>
+        <v>169</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -28204,13 +28226,13 @@
         <v>46</v>
       </c>
       <c r="F5" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="G5" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="H5" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -28222,7 +28244,112 @@
         <v>7</v>
       </c>
       <c r="L5" t="s">
-        <v>62</v>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>-5.5</v>
+      </c>
+      <c r="E6">
+        <v>46</v>
+      </c>
+      <c r="F6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G6" t="s">
+        <v>168</v>
+      </c>
+      <c r="H6" t="s">
+        <v>131</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>7</v>
+      </c>
+      <c r="L6" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>-5.5</v>
+      </c>
+      <c r="E7">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>120</v>
+      </c>
+      <c r="G7" t="s">
+        <v>168</v>
+      </c>
+      <c r="H7" t="s">
+        <v>131</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+      <c r="L7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>174</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>-5.5</v>
+      </c>
+      <c r="E8">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G8" t="s">
+        <v>141</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>7</v>
+      </c>
+      <c r="L8" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -28234,13 +28361,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="33.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
         <v>46</v>
@@ -28249,27 +28380,27 @@
         <v>43</v>
       </c>
       <c r="E1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" t="s">
         <v>64</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>65</v>
-      </c>
-      <c r="G1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -28281,21 +28412,21 @@
         <v>-1</v>
       </c>
       <c r="H2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3759.2140887433002</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -28304,7 +28435,7 @@
         <v>-1</v>
       </c>
       <c r="H3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>
@@ -28323,21 +28454,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AX4"/>
+  <dimension ref="A1:BB6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C1" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D1" t="s">
         <v>43</v>
@@ -28346,180 +28478,192 @@
         <v>46</v>
       </c>
       <c r="F1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I1" t="s">
+        <v>79</v>
+      </c>
+      <c r="J1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K1" t="s">
+        <v>68</v>
+      </c>
+      <c r="L1" t="s">
+        <v>69</v>
+      </c>
+      <c r="M1" t="s">
+        <v>70</v>
+      </c>
+      <c r="N1" t="s">
+        <v>71</v>
+      </c>
+      <c r="O1" t="s">
+        <v>133</v>
+      </c>
+      <c r="P1" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>72</v>
+      </c>
+      <c r="R1" t="s">
+        <v>73</v>
+      </c>
+      <c r="S1" t="s">
+        <v>80</v>
+      </c>
+      <c r="T1" t="s">
+        <v>76</v>
+      </c>
+      <c r="U1" t="s">
+        <v>77</v>
+      </c>
+      <c r="V1" t="s">
+        <v>85</v>
+      </c>
+      <c r="W1" t="s">
+        <v>100</v>
+      </c>
+      <c r="X1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z1" t="s">
         <v>83</v>
       </c>
-      <c r="G1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J1" t="s">
-        <v>69</v>
-      </c>
-      <c r="K1" t="s">
-        <v>70</v>
-      </c>
-      <c r="L1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M1" t="s">
-        <v>72</v>
-      </c>
-      <c r="N1" t="s">
-        <v>73</v>
-      </c>
-      <c r="O1" t="s">
-        <v>142</v>
-      </c>
-      <c r="P1" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>74</v>
-      </c>
-      <c r="R1" t="s">
-        <v>75</v>
-      </c>
-      <c r="S1" t="s">
-        <v>82</v>
-      </c>
-      <c r="T1" t="s">
-        <v>78</v>
-      </c>
-      <c r="U1" t="s">
-        <v>79</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="AA1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC1" t="s">
         <v>87</v>
       </c>
-      <c r="W1" t="s">
-        <v>103</v>
-      </c>
-      <c r="X1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>84</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>88</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>89</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>90</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>91</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>92</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>93</v>
       </c>
-      <c r="AH1" t="s">
-        <v>94</v>
-      </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>95</v>
       </c>
-      <c r="AJ1" t="s">
-        <v>97</v>
-      </c>
       <c r="AK1" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="AL1" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="AM1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="AN1" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="AO1" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="AP1" t="s">
-        <v>110</v>
+        <v>135</v>
       </c>
       <c r="AQ1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AR1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="AS1" t="s">
         <v>106</v>
       </c>
       <c r="AT1" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="AU1" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="AV1" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="AW1" t="s">
-        <v>146</v>
+        <v>109</v>
       </c>
       <c r="AX1" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="2" spans="1:50" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+      <c r="AY1" t="s">
+        <v>178</v>
+      </c>
+      <c r="AZ1" t="s">
+        <v>48</v>
+      </c>
+      <c r="BA1" t="s">
+        <v>137</v>
+      </c>
+      <c r="BB1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="2" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>58</v>
+        <v>165</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>180</v>
       </c>
       <c r="F2">
-        <v>0.96946336745504402</v>
+        <v>0.69</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>0</v>
       </c>
-      <c r="I2" t="s">
-        <v>7</v>
+      <c r="I2">
+        <v>30</v>
       </c>
       <c r="J2">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M2">
-        <v>1000</v>
-      </c>
-      <c r="N2">
-        <v>21000</v>
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>7</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -28528,7 +28672,7 @@
         <v>1</v>
       </c>
       <c r="S2">
-        <v>51869.6104378526</v>
+        <v>79103.134036374293</v>
       </c>
       <c r="T2">
         <v>0</v>
@@ -28540,13 +28684,13 @@
         <v>0</v>
       </c>
       <c r="W2">
-        <v>464.56899717447197</v>
+        <v>0</v>
       </c>
       <c r="X2">
         <v>1</v>
       </c>
       <c r="Y2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -28575,52 +28719,40 @@
       <c r="AJ2">
         <v>0</v>
       </c>
-      <c r="AO2">
-        <v>500</v>
+      <c r="AL2">
+        <v>1</v>
+      </c>
+      <c r="AN2">
+        <v>1</v>
       </c>
       <c r="AP2">
         <v>1</v>
       </c>
-      <c r="AQ2">
+      <c r="BA2" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB2">
         <v>0</v>
       </c>
-      <c r="AR2" t="s">
-        <v>114</v>
-      </c>
-      <c r="AS2" t="s">
-        <v>115</v>
-      </c>
-      <c r="AT2">
-        <v>1</v>
-      </c>
-      <c r="AU2">
-        <v>0.96184305038492401</v>
-      </c>
-      <c r="AW2" t="s">
-        <v>99</v>
-      </c>
-      <c r="AX2">
-        <v>464.56899717447197</v>
-      </c>
-    </row>
-    <row r="3" spans="1:50" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>149</v>
+        <v>181</v>
       </c>
       <c r="B3" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C3" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="E3" t="s">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="F3">
-        <v>0.43</v>
+        <v>1.04</v>
       </c>
       <c r="G3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H3">
         <v>0</v>
@@ -28635,7 +28767,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -28650,10 +28782,10 @@
         <v>1</v>
       </c>
       <c r="S3">
-        <v>19458.581797472601</v>
+        <v>6592.87850802293</v>
       </c>
       <c r="T3">
-        <v>2.0476599999999898</v>
+        <v>0</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -28668,7 +28800,7 @@
         <v>1</v>
       </c>
       <c r="Y3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -28697,52 +28829,55 @@
       <c r="AJ3">
         <v>0</v>
       </c>
-      <c r="AM3" t="s">
-        <v>139</v>
+      <c r="AL3">
+        <v>1</v>
       </c>
       <c r="AN3">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="AW3" t="s">
-        <v>99</v>
-      </c>
-      <c r="AX3">
+        <v>1</v>
+      </c>
+      <c r="AP3">
+        <v>1</v>
+      </c>
+      <c r="BA3" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:50" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:54" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="B4" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="C4" t="s">
-        <v>58</v>
+        <v>169</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>184</v>
       </c>
       <c r="F4">
-        <v>0.6</v>
+        <v>0.94943601711396297</v>
       </c>
       <c r="G4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H4">
         <v>0</v>
       </c>
-      <c r="I4">
-        <v>25</v>
+      <c r="I4" t="s">
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="K4">
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="M4">
         <v>0</v>
@@ -28757,10 +28892,10 @@
         <v>1</v>
       </c>
       <c r="S4">
-        <v>60095.398938164697</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>2.5397399999999899</v>
+        <v>0</v>
       </c>
       <c r="U4">
         <v>0</v>
@@ -28775,7 +28910,7 @@
         <v>1</v>
       </c>
       <c r="Y4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -28804,35 +28939,266 @@
       <c r="AJ4">
         <v>0</v>
       </c>
-      <c r="AM4" t="s">
-        <v>139</v>
+      <c r="AL4">
+        <v>1</v>
       </c>
       <c r="AN4">
-        <v>0.19800000000000001</v>
-      </c>
-      <c r="AW4" t="s">
-        <v>99</v>
-      </c>
-      <c r="AX4">
+        <v>1</v>
+      </c>
+      <c r="AP4">
+        <v>1</v>
+      </c>
+      <c r="AZ4" t="s">
+        <v>131</v>
+      </c>
+      <c r="BA4" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB4">
         <v>0</v>
       </c>
     </row>
+    <row r="5" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" t="s">
+        <v>173</v>
+      </c>
+      <c r="E5" t="s">
+        <v>186</v>
+      </c>
+      <c r="F5">
+        <v>0.87870000000000004</v>
+      </c>
+      <c r="G5" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <v>20</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5" t="s">
+        <v>66</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q5">
+        <v>0.3</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>56809.571943766801</v>
+      </c>
+      <c r="T5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AH5">
+        <v>1</v>
+      </c>
+      <c r="AI5">
+        <v>1</v>
+      </c>
+      <c r="AJ5">
+        <v>0</v>
+      </c>
+      <c r="AL5">
+        <v>1</v>
+      </c>
+      <c r="AN5">
+        <v>1</v>
+      </c>
+      <c r="AP5">
+        <v>1</v>
+      </c>
+      <c r="BA5" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:54" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>174</v>
+      </c>
+      <c r="B6" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" t="s">
+        <v>174</v>
+      </c>
+      <c r="E6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H6">
+        <v>0</v>
+      </c>
+      <c r="I6" t="s">
+        <v>7</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6" t="s">
+        <v>66</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>7</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6">
+        <v>0</v>
+      </c>
+      <c r="V6">
+        <v>0</v>
+      </c>
+      <c r="W6">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>1</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>1</v>
+      </c>
+      <c r="AI6">
+        <v>1</v>
+      </c>
+      <c r="AJ6">
+        <v>0</v>
+      </c>
+      <c r="AL6">
+        <v>1</v>
+      </c>
+      <c r="AN6">
+        <v>1</v>
+      </c>
+      <c r="AP6">
+        <v>1</v>
+      </c>
+      <c r="BA6" t="s">
+        <v>96</v>
+      </c>
+      <c r="BB6">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:BB6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AM2"/>
+  <dimension ref="A1:AO2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
         <v>52</v>
@@ -28841,120 +29207,126 @@
         <v>43</v>
       </c>
       <c r="E1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G1" t="s">
         <v>69</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>70</v>
       </c>
-      <c r="G1" t="s">
+      <c r="I1" t="s">
         <v>71</v>
       </c>
-      <c r="H1" t="s">
+      <c r="J1" t="s">
+        <v>133</v>
+      </c>
+      <c r="K1" t="s">
         <v>72</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>73</v>
       </c>
-      <c r="J1" t="s">
-        <v>142</v>
-      </c>
-      <c r="K1" t="s">
+      <c r="M1" t="s">
+        <v>62</v>
+      </c>
+      <c r="N1" t="s">
         <v>74</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>75</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q1" t="s">
         <v>64</v>
-      </c>
-      <c r="N1" t="s">
-        <v>76</v>
-      </c>
-      <c r="O1" t="s">
-        <v>77</v>
-      </c>
-      <c r="P1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>66</v>
       </c>
       <c r="R1" t="s">
         <v>46</v>
       </c>
       <c r="S1" t="s">
+        <v>76</v>
+      </c>
+      <c r="T1" t="s">
+        <v>77</v>
+      </c>
+      <c r="U1" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" t="s">
         <v>78</v>
       </c>
-      <c r="T1" t="s">
+      <c r="W1" t="s">
         <v>79</v>
       </c>
-      <c r="U1" t="s">
-        <v>67</v>
-      </c>
-      <c r="V1" t="s">
+      <c r="X1" t="s">
         <v>80</v>
       </c>
-      <c r="W1" t="s">
+      <c r="Y1" t="s">
         <v>81</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Z1" t="s">
         <v>82</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="AA1" t="s">
         <v>83</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AB1" t="s">
         <v>84</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AC1" t="s">
         <v>85</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AD1" t="s">
         <v>86</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AE1" t="s">
         <v>87</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AF1" t="s">
         <v>88</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AG1" t="s">
         <v>89</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AH1" t="s">
         <v>90</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AI1" t="s">
         <v>91</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AJ1" t="s">
         <v>92</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AK1" t="s">
         <v>93</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AL1" t="s">
         <v>94</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AM1" t="s">
         <v>95</v>
       </c>
-      <c r="AL1" t="s">
-        <v>96</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+      <c r="AN1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="C2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -28963,7 +29335,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -28978,7 +29350,7 @@
         <v>1</v>
       </c>
       <c r="N2" t="e">
-        <f>-inf</f>
+        <f t="shared" ref="N2" si="0">-inf</f>
         <v>#NAME?</v>
       </c>
       <c r="O2" t="s">
@@ -28991,7 +29363,7 @@
         <v>1</v>
       </c>
       <c r="R2" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="S2">
         <v>24.568000000000001</v>
@@ -29000,7 +29372,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="V2">
         <v>0</v>
@@ -29015,7 +29387,7 @@
         <v>1</v>
       </c>
       <c r="Z2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="AA2">
         <v>0</v>
@@ -29067,20 +29439,20 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="28.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="B1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C1" t="s">
         <v>43</v>
@@ -29089,159 +29461,86 @@
         <v>46</v>
       </c>
       <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" t="s">
+        <v>152</v>
+      </c>
+      <c r="I1" t="s">
+        <v>153</v>
+      </c>
+      <c r="J1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K1" t="s">
+        <v>155</v>
+      </c>
+      <c r="L1" t="s">
+        <v>156</v>
+      </c>
+      <c r="M1" t="s">
+        <v>157</v>
+      </c>
+      <c r="N1" t="s">
+        <v>158</v>
+      </c>
+      <c r="O1" t="s">
         <v>159</v>
       </c>
-      <c r="F1" t="s">
+      <c r="P1" t="s">
         <v>160</v>
       </c>
-      <c r="G1" t="s">
+      <c r="Q1" t="s">
+        <v>62</v>
+      </c>
+      <c r="R1" t="s">
+        <v>63</v>
+      </c>
+      <c r="S1" t="s">
         <v>161</v>
       </c>
-      <c r="H1" t="s">
+      <c r="T1" t="s">
+        <v>64</v>
+      </c>
+      <c r="U1" t="s">
+        <v>76</v>
+      </c>
+      <c r="V1" t="s">
+        <v>77</v>
+      </c>
+      <c r="W1" t="s">
         <v>162</v>
       </c>
-      <c r="I1" t="s">
+      <c r="X1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y1" t="s">
         <v>163</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Z1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>79</v>
+      </c>
+      <c r="AC1" t="s">
         <v>164</v>
       </c>
-      <c r="K1" t="s">
-        <v>165</v>
-      </c>
-      <c r="L1" t="s">
-        <v>166</v>
-      </c>
-      <c r="M1" t="s">
-        <v>167</v>
-      </c>
-      <c r="N1" t="s">
-        <v>168</v>
-      </c>
-      <c r="O1" t="s">
-        <v>169</v>
-      </c>
-      <c r="P1" t="s">
-        <v>170</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R1" t="s">
-        <v>65</v>
-      </c>
-      <c r="S1" t="s">
-        <v>171</v>
-      </c>
-      <c r="T1" t="s">
-        <v>66</v>
-      </c>
-      <c r="U1" t="s">
-        <v>78</v>
-      </c>
-      <c r="V1" t="s">
-        <v>79</v>
-      </c>
-      <c r="W1" t="s">
-        <v>172</v>
-      </c>
-      <c r="X1" t="s">
-        <v>82</v>
-      </c>
-      <c r="Y1" t="s">
-        <v>173</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>80</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>81</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>139</v>
-      </c>
-      <c r="B2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E2">
-        <v>100000000</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2" t="s">
-        <v>99</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>100000000</v>
-      </c>
-      <c r="K2">
-        <v>-1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>99</v>
-      </c>
-      <c r="O2" t="s">
-        <v>99</v>
-      </c>
-      <c r="P2" t="s">
-        <v>99</v>
-      </c>
-      <c r="R2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
-      </c>
-      <c r="U2">
-        <v>-300</v>
-      </c>
-      <c r="V2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>0</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>68</v>
-      </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>7</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
+      <c r="AD1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AD1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -29253,202 +29552,202 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>58</v>
+        <v>144</v>
       </c>
       <c r="B1" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>22096.8054733276</v>
+      <c r="A2" s="1">
+        <v>43466</v>
       </c>
       <c r="B2">
-        <v>753.19456481933503</v>
+        <v>21244.721737339001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>20888.008621215798</v>
+      <c r="A3" s="1">
+        <v>43466.041666666664</v>
       </c>
       <c r="B3">
-        <v>711.99136352539006</v>
+        <v>21829.205770521101</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>19587.343338012601</v>
+      <c r="A4" s="1">
+        <v>43466.083333333336</v>
       </c>
       <c r="B4">
-        <v>667.65670776367097</v>
+        <v>23923.2027827846</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>18817.581481933499</v>
+      <c r="A5" s="1">
+        <v>43466.125</v>
       </c>
       <c r="B5">
-        <v>641.41851043701104</v>
+        <v>29835.824722945101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>18860.131164550701</v>
+      <c r="A6" s="1">
+        <v>43466.166666666664</v>
       </c>
       <c r="B6">
-        <v>642.868858337402</v>
+        <v>39361.634530993797</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>19708.222991943301</v>
+      <c r="A7" s="1">
+        <v>43466.208333333336</v>
       </c>
       <c r="B7">
-        <v>671.77701568603504</v>
+        <v>41875.113789239498</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>20146.290946960398</v>
+      <c r="A8" s="1">
+        <v>43466.25</v>
       </c>
       <c r="B8">
-        <v>686.70906829833905</v>
+        <v>40045.018286544102</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>20500.2266769409</v>
+      <c r="A9" s="1">
+        <v>43466.291666666664</v>
       </c>
       <c r="B9">
-        <v>698.77337646484295</v>
+        <v>38167.330863204799</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>21604.583358764601</v>
+      <c r="A10" s="1">
+        <v>43466.333333333336</v>
       </c>
       <c r="B10">
-        <v>736.41661071777298</v>
+        <v>36317.040005582101</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>22913.9521331787</v>
+      <c r="A11" s="1">
+        <v>43466.375</v>
       </c>
       <c r="B11">
-        <v>781.04792022704999</v>
+        <v>34499.809763646197</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>23737.867950439399</v>
+      <c r="A12" s="1">
+        <v>43466.416666666664</v>
       </c>
       <c r="B12">
-        <v>809.13202667236305</v>
+        <v>33235.789462595298</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>24342.2664260864</v>
+      <c r="A13" s="1">
+        <v>43466.458333333336</v>
       </c>
       <c r="B13">
-        <v>829.73361968994095</v>
+        <v>32411.059479493601</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>23179.887351989699</v>
+      <c r="A14" s="1">
+        <v>43466.5</v>
       </c>
       <c r="B14">
-        <v>790.11264038085903</v>
+        <v>31798.576271805301</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15">
-        <v>22326.960304260199</v>
+      <c r="A15" s="1">
+        <v>43466.541666666664</v>
       </c>
       <c r="B15">
-        <v>761.039649963378</v>
+        <v>31711.114158543001</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>22780.5009613037</v>
+      <c r="A16" s="1">
+        <v>43466.583333333336</v>
       </c>
       <c r="B16">
-        <v>776.49910736083905</v>
+        <v>31951.545912430101</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17">
-        <v>24151.7599487304</v>
+      <c r="A17" s="1">
+        <v>43466.625</v>
       </c>
       <c r="B17">
-        <v>823.24002075195301</v>
+        <v>32883.285760600702</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>27578.9406433105</v>
+      <c r="A18" s="1">
+        <v>43466.666666666664</v>
       </c>
       <c r="B18">
-        <v>940.059326171875</v>
+        <v>33709.643568735701</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19">
-        <v>28767.4296875</v>
+      <c r="A19" s="1">
+        <v>43466.708333333336</v>
       </c>
       <c r="B19">
-        <v>980.5703125</v>
+        <v>34524.370481024998</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>29461.762512206999</v>
+      <c r="A20" s="1">
+        <v>43466.75</v>
       </c>
       <c r="B20">
-        <v>1004.23742675781</v>
+        <v>34772.389644686802</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21">
-        <v>28889.2763671875</v>
+      <c r="A21" s="1">
+        <v>43466.791666666664</v>
       </c>
       <c r="B21">
-        <v>984.72360229492097</v>
+        <v>33887.053195171196</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22">
-        <v>27626.3254547119</v>
+      <c r="A22" s="1">
+        <v>43466.833333333336</v>
       </c>
       <c r="B22">
-        <v>941.67448425292901</v>
+        <v>30746.434366830399</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23">
-        <v>25685.481361389098</v>
+      <c r="A23" s="1">
+        <v>43466.875</v>
       </c>
       <c r="B23">
-        <v>875.51863861083905</v>
+        <v>26206.653202087899</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24">
-        <v>23116.062927245999</v>
+      <c r="A24" s="1">
+        <v>43466.916666666664</v>
       </c>
       <c r="B24">
-        <v>787.93709564208905</v>
+        <v>22006.013570847099</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25">
-        <v>20935.393531799298</v>
+      <c r="A25" s="1">
+        <v>43466.958333333336</v>
       </c>
       <c r="B25">
-        <v>713.60652160644497</v>
+        <v>20525.349307217701</v>
       </c>
     </row>
   </sheetData>
